--- a/Data Set/Teamsync_testcases.xlsx
+++ b/Data Set/Teamsync_testcases.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,8 +138,15 @@
       <b val="1"/>
       <color rgb="00006100"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -193,6 +200,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -249,7 +261,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -444,6 +456,22 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7726,7 +7754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="7.90625" bestFit="1" customWidth="1" style="34" min="1" max="1"/>
@@ -7798,6 +7826,11 @@
           <t>DATA SET</t>
         </is>
       </c>
+      <c r="L1" s="76" t="inlineStr">
+        <is>
+          <t>Script Status Code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="32" t="inlineStr">
@@ -7847,9 +7880,14 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J3" s="65" t="inlineStr">
+      <c r="J3" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>200 OK</t>
         </is>
       </c>
     </row>
@@ -7894,9 +7932,14 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J4" s="65" t="inlineStr">
+      <c r="J4" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>200 OK</t>
         </is>
       </c>
     </row>
@@ -7941,9 +7984,14 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J5" s="65" t="inlineStr">
+      <c r="J5" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>200 OK</t>
         </is>
       </c>
     </row>
@@ -7988,11 +8036,12 @@
           <t xml:space="preserve"> - </t>
         </is>
       </c>
-      <c r="J6" s="31" t="inlineStr">
+      <c r="J6" s="73" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
@@ -8035,9 +8084,14 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J7" s="65" t="inlineStr">
+      <c r="J7" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>200 OK</t>
         </is>
       </c>
     </row>
@@ -8082,9 +8136,14 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="J8" s="65" t="inlineStr">
+      <c r="J8" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
         </is>
       </c>
     </row>
@@ -8129,9 +8188,14 @@
           <t>404 Not Found</t>
         </is>
       </c>
-      <c r="J9" s="65" t="inlineStr">
+      <c r="J9" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>404 Not Found</t>
         </is>
       </c>
     </row>
@@ -8176,9 +8240,14 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="J10" s="65" t="inlineStr">
+      <c r="J10" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>500 Internal Server Error</t>
         </is>
       </c>
     </row>
@@ -8223,9 +8292,14 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="J11" s="65" t="inlineStr">
+      <c r="J11" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
         </is>
       </c>
     </row>
@@ -8270,9 +8344,14 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="J12" s="65" t="inlineStr">
+      <c r="J12" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>500 Internal Server Error</t>
         </is>
       </c>
     </row>
@@ -8317,9 +8396,14 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="J13" s="65" t="inlineStr">
+      <c r="J13" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>404 Not Found</t>
         </is>
       </c>
     </row>
@@ -8364,11 +8448,12 @@
           <t>423 Locked</t>
         </is>
       </c>
-      <c r="J14" s="31" t="inlineStr">
+      <c r="J14" s="73" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
@@ -8411,9 +8496,14 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="J15" s="65" t="inlineStr">
+      <c r="J15" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>200 OK</t>
         </is>
       </c>
     </row>
@@ -8458,11 +8548,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J16" s="65" t="inlineStr">
+      <c r="J16" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="51" t="inlineStr">
@@ -8505,11 +8596,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J17" s="65" t="inlineStr">
+      <c r="J17" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18" ht="29" customHeight="1" s="34">
       <c r="B18" s="2" t="inlineStr">
@@ -8552,11 +8644,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J18" s="65" t="inlineStr">
+      <c r="J18" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19" ht="29" customHeight="1" s="34">
       <c r="B19" s="2" t="inlineStr">
@@ -8599,11 +8692,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J19" s="65" t="inlineStr">
+      <c r="J19" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20" ht="29" customHeight="1" s="34">
       <c r="B20" s="2" t="inlineStr">
@@ -8646,9 +8740,14 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="J20" s="65" t="inlineStr">
+      <c r="J20" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
         </is>
       </c>
     </row>
@@ -8693,9 +8792,14 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J21" s="65" t="inlineStr">
+      <c r="J21" s="72" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>200 OK</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="7.90625" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -8785,6 +8889,11 @@
           <t>Data set</t>
         </is>
       </c>
+      <c r="L1" s="76" t="inlineStr">
+        <is>
+          <t>Script Status Code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -8850,7 +8959,7 @@
 200 OK</t>
         </is>
       </c>
-      <c r="J3" s="66" t="inlineStr">
+      <c r="J3" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8860,6 +8969,7 @@
           <t>Upload .png file</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4" ht="72.5" customHeight="1" s="34">
       <c r="A4" s="43" t="n"/>
@@ -8908,7 +9018,7 @@
 200 OK</t>
         </is>
       </c>
-      <c r="J4" s="66" t="inlineStr">
+      <c r="J4" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8918,6 +9028,7 @@
           <t>Upload .jpg file</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5" ht="72.5" customHeight="1" s="34">
       <c r="A5" s="43" t="n"/>
@@ -8966,7 +9077,7 @@
 200 OK</t>
         </is>
       </c>
-      <c r="J5" s="66" t="inlineStr">
+      <c r="J5" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8976,6 +9087,7 @@
           <t>Upload .pdf file</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6" ht="72.5" customHeight="1" s="34">
       <c r="A6" s="43" t="n"/>
@@ -9024,7 +9136,7 @@
 200 OK</t>
         </is>
       </c>
-      <c r="J6" s="66" t="inlineStr">
+      <c r="J6" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9034,6 +9146,7 @@
           <t>Upload .docx file</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7" ht="72.5" customHeight="1" s="34">
       <c r="A7" s="43" t="n"/>
@@ -9082,7 +9195,7 @@
 200 OK</t>
         </is>
       </c>
-      <c r="J7" s="66" t="inlineStr">
+      <c r="J7" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9092,6 +9205,7 @@
           <t>Upload .xls file</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8" ht="29" customHeight="1" s="34">
       <c r="A8" s="43" t="n"/>
@@ -9135,7 +9249,7 @@
           <t>If fails → Upload failed. Please try again</t>
         </is>
       </c>
-      <c r="J8" s="66" t="inlineStr">
+      <c r="J8" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9145,6 +9259,7 @@
           <t>Upload 0bytes/No content .pdf file</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9" ht="43.5" customHeight="1" s="34">
       <c r="A9" s="43" t="n"/>
@@ -9188,14 +9303,19 @@
           <t>If rejected → "File size exceeds limit" (incorrect behavior)</t>
         </is>
       </c>
-      <c r="J9" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J9" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K9" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Upload large file  .pdf </t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
         </is>
       </c>
     </row>
@@ -9251,6 +9371,7 @@
           <t>Upload 0bytes/No content .pdf file</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="43" t="n"/>
@@ -9294,7 +9415,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J11" s="66" t="inlineStr">
+      <c r="J11" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9304,6 +9425,7 @@
           <t>Upload single file (.pdf)</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="43" t="n"/>
@@ -9347,7 +9469,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J12" s="66" t="inlineStr">
+      <c r="J12" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9357,6 +9479,7 @@
           <t>Upload Multiple file (.pdf)</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="43" t="n"/>
@@ -9400,12 +9523,17 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J13" s="66" t="inlineStr">
+      <c r="J13" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="K13" s="43" t="n"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="43" t="n"/>
@@ -9449,7 +9577,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J14" s="66" t="inlineStr">
+      <c r="J14" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9459,6 +9587,7 @@
           <t>Upload file (.pdf)</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15" ht="29" customHeight="1" s="34">
       <c r="A15" s="43" t="n"/>
@@ -9502,7 +9631,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J15" s="67" t="inlineStr">
+      <c r="J15" s="74" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -9512,6 +9641,7 @@
           <t>Upload file (.pdf) and downlaod same file</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="43" t="n"/>
@@ -9555,9 +9685,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J16" s="68" t="inlineStr">
-        <is>
-          <t>Skipped</t>
+      <c r="J16" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K16" s="43" t="inlineStr">
@@ -9565,6 +9695,7 @@
           <t>Upload file (.pdf) and delete same file</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="43" t="n"/>
@@ -9608,7 +9739,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J17" s="66" t="inlineStr">
+      <c r="J17" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9618,6 +9749,7 @@
           <t xml:space="preserve">Upload file (.pdf) </t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18" ht="29" customHeight="1" s="34">
       <c r="A18" s="43" t="n"/>
@@ -9661,14 +9793,19 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J18" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J18" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K18" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Upload file (.pdf) </t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>500 Internal Server Error</t>
         </is>
       </c>
     </row>
@@ -9714,7 +9851,7 @@
           <t>415 Unsupported Media Type/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J19" s="66" t="inlineStr">
+      <c r="J19" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9722,6 +9859,11 @@
       <c r="K19" s="43" t="inlineStr">
         <is>
           <t>Uplaod .txt file</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9909,7 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J20" s="66" t="inlineStr">
+      <c r="J20" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9775,6 +9917,11 @@
       <c r="K20" s="43" t="inlineStr">
         <is>
           <t>Upload 0kb.pdf file</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
         </is>
       </c>
     </row>
@@ -9820,9 +9967,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J21" s="67" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="J21" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K21" s="43" t="inlineStr">
@@ -9830,6 +9977,7 @@
           <t>Upload pdf, docx, xlsx, ppt</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="43" t="n"/>
@@ -9873,12 +10021,17 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="J22" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J22" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K22" s="43" t="n"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>500 Internal Server Error</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="29" customHeight="1" s="34">
       <c r="A23" s="43" t="n"/>
@@ -9928,6 +10081,7 @@
         </is>
       </c>
       <c r="K23" s="43" t="n"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="43" t="n"/>
@@ -9971,9 +10125,9 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="J24" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J24" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K24" s="43" t="inlineStr">
@@ -9981,6 +10135,7 @@
           <t>Pdf file download successfully</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="43" t="n"/>
@@ -10024,12 +10179,13 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="J25" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J25" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K25" s="43" t="n"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26" ht="29" customHeight="1" s="34">
       <c r="A26" s="43" t="n"/>
@@ -10073,12 +10229,17 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="J26" s="66" t="inlineStr">
+      <c r="J26" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="K26" s="43" t="n"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="43" t="n"/>
@@ -10122,12 +10283,13 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="J27" s="69" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J27" s="77" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K27" s="44" t="n"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28" ht="43.5" customHeight="1" s="34">
       <c r="A28" s="43" t="n"/>
@@ -10171,7 +10333,7 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J28" s="66" t="inlineStr">
+      <c r="J28" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10179,6 +10341,11 @@
       <c r="K28" s="43" t="inlineStr">
         <is>
           <t>Upload .exe file</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10391,7 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J29" s="66" t="inlineStr">
+      <c r="J29" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10232,6 +10399,11 @@
       <c r="K29" s="43" t="inlineStr">
         <is>
           <t>Upload .bat file</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>403 Forbidden</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10449,7 @@
           <t>415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="J30" s="66" t="inlineStr">
+      <c r="J30" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10285,6 +10457,11 @@
       <c r="K30" s="43" t="inlineStr">
         <is>
           <t>Upload .js file</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
         </is>
       </c>
     </row>
@@ -10330,12 +10507,17 @@
           <t xml:space="preserve"> Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J31" s="66" t="inlineStr">
+      <c r="J31" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="K31" s="43" t="n"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="43.5" customHeight="1" s="34">
       <c r="A32" s="43" t="n"/>
@@ -10379,7 +10561,7 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J32" s="66" t="inlineStr">
+      <c r="J32" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10387,6 +10569,11 @@
       <c r="K32" s="43" t="inlineStr">
         <is>
           <t>Uplaod without extension file (large-doc)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
         </is>
       </c>
     </row>
@@ -10433,7 +10620,7 @@
 </t>
         </is>
       </c>
-      <c r="J33" s="66" t="inlineStr">
+      <c r="J33" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10441,6 +10628,11 @@
       <c r="K33" s="43" t="inlineStr">
         <is>
           <t>File.PDF, Test.PDF, Sample.DOCX</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10678,7 @@
           <t>/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J34" s="66" t="inlineStr">
+      <c r="J34" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10494,6 +10686,11 @@
       <c r="K34" s="43" t="inlineStr">
         <is>
           <t>File.pdf.png, Test.docx.pdf</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10736,7 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J35" s="66" t="inlineStr">
+      <c r="J35" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10547,6 +10744,11 @@
       <c r="K35" s="43" t="inlineStr">
         <is>
           <t>Large-doc.pdf convert to Large-doc.png</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
         </is>
       </c>
     </row>
@@ -10602,6 +10804,7 @@
           <t>test.pdf → test.png</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37" ht="29" customHeight="1" s="34">
       <c r="A37" s="43" t="n"/>
@@ -10645,9 +10848,9 @@
           <t>415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="J37" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J37" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K37" s="43" t="inlineStr">
@@ -10655,6 +10858,7 @@
           <t>Protected with password .xlsx file</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38" ht="29" customHeight="1" s="34">
       <c r="A38" s="43" t="n"/>
@@ -10698,9 +10902,9 @@
           <t>415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="J38" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J38" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K38" s="43" t="inlineStr">
@@ -10708,6 +10912,7 @@
           <t>Protected with password .xlsx file</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39" ht="29" customHeight="1" s="34">
       <c r="A39" s="43" t="n"/>
@@ -10751,7 +10956,7 @@
           <t>200 OK / 415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="J39" s="66" t="inlineStr">
+      <c r="J39" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10759,6 +10964,11 @@
       <c r="K39" s="43" t="inlineStr">
         <is>
           <t>Upload .zip file</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>200 OK</t>
         </is>
       </c>
     </row>
@@ -10804,9 +11014,9 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="J40" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J40" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K40" s="43" t="inlineStr">
@@ -10814,6 +11024,7 @@
           <t>Upload .zip file</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="43" t="n"/>
@@ -10857,7 +11068,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J41" s="66" t="inlineStr">
+      <c r="J41" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10865,6 +11076,11 @@
       <c r="K41" s="43" t="inlineStr">
         <is>
           <t>Upload .Html file</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>403 Forbidden</t>
         </is>
       </c>
     </row>
@@ -10910,7 +11126,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J42" s="66" t="inlineStr">
+      <c r="J42" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10918,6 +11134,11 @@
       <c r="K42" s="43" t="inlineStr">
         <is>
           <t>Upload .svg file</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>200 OK</t>
         </is>
       </c>
     </row>
@@ -10963,9 +11184,9 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J43" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J43" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K43" s="43" t="inlineStr">
@@ -10973,6 +11194,7 @@
           <t>Upload .pdf file</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44" ht="29" customHeight="1" s="34">
       <c r="A44" s="43" t="n"/>
@@ -11016,9 +11238,9 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J44" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J44" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K44" s="43" t="inlineStr">
@@ -11026,6 +11248,7 @@
           <t>Upload .pdf file</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45" ht="43.5" customHeight="1" s="34">
       <c r="A45" s="43" t="n"/>
@@ -11069,9 +11292,9 @@
           <t>413 Payload Too Large/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="J45" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J45" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K45" s="43" t="inlineStr">
@@ -11079,6 +11302,7 @@
           <t>Upload exceed limit .pdf file</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46" ht="29" customHeight="1" s="34">
       <c r="A46" s="43" t="n"/>
@@ -11122,7 +11346,7 @@
           <t>400 Bad Request/415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="J46" s="66" t="inlineStr">
+      <c r="J46" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11130,6 +11354,11 @@
       <c r="K46" s="43" t="inlineStr">
         <is>
           <t>Upload 0kb.pdf file</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
         </is>
       </c>
     </row>
@@ -11175,12 +11404,13 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J47" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J47" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K47" s="43" t="n"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48" ht="29" customHeight="1" s="34">
       <c r="A48" s="43" t="n"/>
@@ -11224,9 +11454,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J48" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J48" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K48" s="43" t="inlineStr">
@@ -11234,6 +11464,7 @@
           <t>Upload .pdf file</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="43" t="n"/>
@@ -11277,9 +11508,9 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="J49" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J49" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K49" s="43" t="inlineStr">
@@ -11287,6 +11518,7 @@
           <t>Upload .pdf file</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="43" t="n"/>
@@ -11330,9 +11562,9 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="J50" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J50" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K50" s="43" t="inlineStr">
@@ -11340,6 +11572,7 @@
           <t>Upload .pdf file</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51" ht="29" customHeight="1" s="34">
       <c r="A51" s="43" t="n"/>
@@ -11383,9 +11616,9 @@
           <t>Uplaod Successfully</t>
         </is>
       </c>
-      <c r="J51" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J51" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K51" s="43" t="inlineStr">
@@ -11393,6 +11626,7 @@
           <t>Upload .pdf file</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52" ht="29" customHeight="1" s="34">
       <c r="A52" s="43" t="n"/>
@@ -11436,7 +11670,7 @@
           <t>200/400</t>
         </is>
       </c>
-      <c r="J52" s="66" t="inlineStr">
+      <c r="J52" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11444,6 +11678,11 @@
       <c r="K52" s="49" t="inlineStr">
         <is>
           <t>Upload@#$ .pdf file</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
         </is>
       </c>
     </row>
@@ -11489,7 +11728,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J53" s="66" t="inlineStr">
+      <c r="J53" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11497,6 +11736,11 @@
       <c r="K53" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Rename a .png file </t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
         </is>
       </c>
     </row>
@@ -11542,12 +11786,17 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J54" s="66" t="inlineStr">
+      <c r="J54" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="K54" s="43" t="n"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="29" customHeight="1" s="34">
       <c r="A55" s="43" t="n"/>
@@ -11591,7 +11840,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J55" s="66" t="inlineStr">
+      <c r="J55" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11599,6 +11848,11 @@
       <c r="K55" s="41" t="inlineStr">
         <is>
           <t>Upload pdf file swdecvfedwedfvedfdefv.pfd</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11898,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J56" s="66" t="inlineStr">
+      <c r="J56" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11652,6 +11906,11 @@
       <c r="K56" s="43" t="inlineStr">
         <is>
           <t>Upload हिंदी.png file</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
         </is>
       </c>
     </row>
@@ -11697,7 +11956,7 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J57" s="66" t="inlineStr">
+      <c r="J57" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11705,6 +11964,11 @@
       <c r="K57" s="43" t="inlineStr">
         <is>
           <t>Upload 😊.png file</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
         </is>
       </c>
     </row>
@@ -11750,7 +12014,7 @@
           <t>409 Conflict</t>
         </is>
       </c>
-      <c r="J58" s="66" t="inlineStr">
+      <c r="J58" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11758,6 +12022,11 @@
       <c r="K58" s="43" t="inlineStr">
         <is>
           <t>Uplaod same file name</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
         </is>
       </c>
     </row>
@@ -11803,12 +12072,13 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J59" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J59" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K59" s="43" t="n"/>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="43" t="n"/>
@@ -11852,12 +12122,13 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="J60" s="47" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="J60" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K60" s="43" t="n"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="43" t="n"/>
@@ -11901,12 +12172,13 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J61" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J61" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K61" s="43" t="n"/>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="43" t="n"/>
@@ -11950,12 +12222,13 @@
           <t>Canceled (client-side)</t>
         </is>
       </c>
-      <c r="J62" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J62" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K62" s="43" t="n"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="43" t="n"/>
@@ -11999,9 +12272,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J63" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J63" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K63" s="43" t="inlineStr">
@@ -12009,6 +12282,7 @@
           <t>Upload .pdf file</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="43" t="n"/>
@@ -12052,12 +12326,17 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="J64" s="66" t="inlineStr">
+      <c r="J64" s="70" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
       <c r="K64" s="43" t="n"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>415 Unsupported Media Type</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="43" t="n"/>
@@ -12101,12 +12380,13 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="J65" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J65" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K65" s="43" t="n"/>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="43" t="n"/>
@@ -12150,12 +12430,13 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="J66" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J66" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K66" s="43" t="n"/>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="43" t="n"/>
@@ -12199,9 +12480,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J67" s="66" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J67" s="74" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="K67" s="43" t="inlineStr">
@@ -12209,6 +12490,7 @@
           <t>Uplaod .pdf file</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="43" t="n"/>
@@ -12252,9 +12534,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J68" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J68" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K68" s="43" t="inlineStr">
@@ -12262,6 +12544,7 @@
           <t>Uplaod .pdf file</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="43" t="n"/>
@@ -12305,9 +12588,9 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="J69" s="42" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="J69" s="71" t="inlineStr">
+        <is>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="K69" s="43" t="inlineStr">
@@ -12315,6 +12598,7 @@
           <t>Delete .pdf, docx, png file</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="43" t="n"/>
